--- a/exports/trend_1d/VMM_full_report.xlsx
+++ b/exports/trend_1d/VMM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>18.69</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45705</v>
+        <v>45706</v>
       </c>
       <c r="H2" t="n">
-        <v>102.72</v>
+        <v>101.29</v>
       </c>
       <c r="I2" t="n">
         <v>102.5397183883597</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.32</v>
+        <v>-5.65</v>
       </c>
       <c r="L2" t="n">
         <v>9.4</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>19.73</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H3" t="n">
-        <v>108.67</v>
+        <v>112.87</v>
       </c>
       <c r="I3" t="n">
         <v>111.8728987598954</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.29</v>
+        <v>-11.43</v>
       </c>
       <c r="L3" t="n">
-        <v>9.83</v>
+        <v>11.87</v>
       </c>
       <c r="M3" t="n">
         <v>2.02</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>12.43</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="H4" t="n">
-        <v>140.23</v>
+        <v>137.21</v>
       </c>
       <c r="I4" t="n">
         <v>139.2815360924749</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K4" t="n">
-        <v>24.24</v>
+        <v>21.56</v>
       </c>
       <c r="L4" t="n">
         <v>6.71</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.65</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="H5" t="n">
-        <v>122.97</v>
+        <v>127.53</v>
       </c>
       <c r="I5" t="n">
         <v>126.4115601196669</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K5" t="n">
-        <v>10.38</v>
+        <v>7.05</v>
       </c>
       <c r="L5" t="n">
         <v>3.86</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>10.08</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H6" t="n">
-        <v>117.23</v>
+        <v>111.62</v>
       </c>
       <c r="I6" t="n">
         <v>114.6757219054865</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.08</v>
+        <v>-12.48</v>
       </c>
       <c r="L6" t="n">
-        <v>9.210000000000001</v>
+        <v>13.35</v>
       </c>
       <c r="M6" t="n">
         <v>6.82</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>13.64</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H7" t="n">
-        <v>112.52</v>
+        <v>116.59</v>
       </c>
       <c r="I7" t="n">
         <v>114.9311720328651</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-4.45</v>
       </c>
       <c r="L7" t="n">
-        <v>3.61</v>
+        <v>5.12</v>
       </c>
       <c r="M7" t="n">
-        <v>3.54</v>
+        <v>3.85</v>
       </c>
       <c r="N7" t="n">
         <v>7.27</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.83</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="H8" t="n">
-        <v>114.28</v>
+        <v>113.94</v>
       </c>
       <c r="I8" t="n">
         <v>114.1686030349478</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.98</v>
+        <v>-2.27</v>
       </c>
       <c r="L8" t="n">
         <v>5.54</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>8.5</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="H9" t="n">
-        <v>103.43</v>
+        <v>113.5</v>
       </c>
       <c r="I9" t="n">
         <v>111.186887730092</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K9" t="n">
-        <v>9.220000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="L9" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7</v>
+        <v>5.58</v>
       </c>
       <c r="N9" t="n">
-        <v>3.83</v>
+        <v>9.74</v>
       </c>
       <c r="O9" t="n">
         <v>-0.3</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>10.68</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="H10" t="n">
-        <v>103.4</v>
+        <v>101.71</v>
       </c>
       <c r="I10" t="n">
         <v>101.929183844763</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>-8.9</v>
+        <v>-10.39</v>
       </c>
       <c r="L10" t="n">
-        <v>9.68</v>
+        <v>10.96</v>
       </c>
       <c r="M10" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="N10" t="n">
         <v>3.7</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1071,6 +1202,14 @@
       <c r="Q11" t="n">
         <v>31</v>
       </c>
+      <c r="R11" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1983,7 +2122,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1993,7 +2132,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -2003,7 +2142,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8">
@@ -2013,7 +2152,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -2023,7 +2162,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
@@ -2033,7 +2172,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125.4</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="11">
@@ -2073,7 +2212,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.38</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="15">
@@ -2083,7 +2222,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.19</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="16">
@@ -2093,7 +2232,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.88</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="17">
@@ -2103,7 +2242,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.24</v>
+        <v>21.56</v>
       </c>
     </row>
     <row r="18">
@@ -2123,7 +2262,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.56</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="20">
@@ -2143,7 +2282,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.83</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="22">
@@ -2153,7 +2292,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -2163,7 +2302,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2173,7 +2312,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.53</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -2193,7 +2332,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.08</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="27">
@@ -2203,7 +2342,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.65</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="28">
@@ -2213,7 +2352,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
